--- a/ig/hospitalnotification/StructureDefinition-medcom-hospitalNotification-encounter.xlsx
+++ b/ig/hospitalnotification/StructureDefinition-medcom-hospitalNotification-encounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="535">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T09:56:15+01:00</t>
+    <t>2026-02-10T12:55:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>MedCom (http://www.medcom.dk)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -267,6 +267,10 @@
   </si>
   <si>
     <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}medcom-hospitalNotification-6:When the status = 'onleave', the timestamp for beginning of a leave (extension.valuePeriod.start) shall be present. {where(status = 'onleave').extension.value.start.exists() or status != 'onleave'}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1797,10 +1801,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1993,17 +1997,17 @@
   <dimension ref="A1:AN92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.66015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.98828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.76953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.89453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.03125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="117.2265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="101.6796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2012,26 +2016,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="72.99609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="86.171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.171875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.98828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.90625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="137.703125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="184.87890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="163.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2253,13 +2257,13 @@
         <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>79</v>
@@ -2270,10 +2274,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2284,7 +2288,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>79</v>
@@ -2293,19 +2297,19 @@
         <v>79</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2355,13 +2359,13 @@
         <v>79</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>79</v>
@@ -2384,10 +2388,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2398,7 +2402,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>79</v>
@@ -2407,16 +2411,16 @@
         <v>79</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2467,19 +2471,19 @@
         <v>79</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>79</v>
@@ -2496,10 +2500,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2510,28 +2514,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2581,19 +2585,19 @@
         <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>79</v>
@@ -2610,10 +2614,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2624,7 +2628,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>79</v>
@@ -2636,16 +2640,16 @@
         <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2671,13 +2675,13 @@
         <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>79</v>
@@ -2695,19 +2699,19 @@
         <v>79</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>79</v>
@@ -2724,21 +2728,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>79</v>
@@ -2750,16 +2754,16 @@
         <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2809,25 +2813,25 @@
         <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>79</v>
@@ -2838,14 +2842,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2864,16 +2868,16 @@
         <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2923,7 +2927,7 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2941,7 +2945,7 @@
         <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>79</v>
@@ -2952,10 +2956,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2978,13 +2982,13 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3023,17 +3027,17 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -3045,7 +3049,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -3060,15 +3064,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -3078,25 +3082,25 @@
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3147,7 +3151,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3156,10 +3160,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -3176,14 +3180,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3196,25 +3200,25 @@
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
@@ -3263,7 +3267,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3275,13 +3279,13 @@
         <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3292,10 +3296,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3315,16 +3319,16 @@
         <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3375,7 +3379,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3387,27 +3391,27 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3415,31 +3419,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3465,11 +3469,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3487,39 +3491,39 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3542,16 +3546,16 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3601,7 +3605,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3613,13 +3617,13 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -3630,10 +3634,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3644,7 +3648,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3656,13 +3660,13 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3713,13 +3717,13 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
@@ -3731,7 +3735,7 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -3742,14 +3746,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3768,16 +3772,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3827,7 +3831,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3839,13 +3843,13 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3856,14 +3860,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3876,25 +3880,25 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3943,7 +3947,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3955,13 +3959,13 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3972,10 +3976,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3983,10 +3987,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -3998,13 +4002,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4031,13 +4035,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4055,25 +4059,25 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -4084,10 +4088,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4095,10 +4099,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4110,13 +4114,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4167,25 +4171,25 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4194,12 +4198,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4207,28 +4211,28 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4255,11 +4259,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4277,39 +4281,39 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4332,13 +4336,13 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4389,7 +4393,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4401,13 +4405,13 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4418,10 +4422,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4432,7 +4436,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4444,13 +4448,13 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4501,13 +4505,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4519,7 +4523,7 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4530,14 +4534,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4556,16 +4560,16 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4615,7 +4619,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4627,13 +4631,13 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4644,14 +4648,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4664,25 +4668,25 @@
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4731,7 +4735,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4743,13 +4747,13 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -4760,10 +4764,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4771,10 +4775,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4786,13 +4790,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4819,13 +4823,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4843,25 +4847,25 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4872,10 +4876,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4883,10 +4887,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4898,13 +4902,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4955,25 +4959,25 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4984,10 +4988,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5007,19 +5011,19 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5045,13 +5049,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -5069,7 +5073,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5081,27 +5085,27 @@
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5121,16 +5125,16 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5157,13 +5161,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5181,39 +5185,39 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5236,13 +5240,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5269,13 +5273,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5293,71 +5297,71 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5407,39 +5411,39 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5447,28 +5451,28 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5507,17 +5511,17 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5529,27 +5533,27 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5560,7 +5564,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5572,13 +5576,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5629,13 +5633,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -5647,7 +5651,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5658,14 +5662,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5684,16 +5688,16 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5731,19 +5735,19 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5755,13 +5759,13 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5772,10 +5776,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5795,19 +5799,19 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5857,25 +5861,25 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5886,10 +5890,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5900,7 +5904,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -5909,19 +5913,19 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5947,13 +5951,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5971,25 +5975,25 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -5998,12 +6002,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6011,31 +6015,31 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6085,25 +6089,25 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -6114,10 +6118,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6128,7 +6132,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6137,19 +6141,19 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6199,25 +6203,25 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6226,15 +6230,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -6244,25 +6248,25 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6313,7 +6317,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6325,27 +6329,27 @@
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6356,7 +6360,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6368,13 +6372,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6425,13 +6429,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6443,7 +6447,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6454,14 +6458,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6480,16 +6484,16 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6527,19 +6531,19 @@
         <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6551,13 +6555,13 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6568,10 +6572,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6591,19 +6595,19 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6653,25 +6657,25 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6682,10 +6686,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6696,7 +6700,7 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6705,19 +6709,19 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6743,13 +6747,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6767,25 +6771,25 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6796,10 +6800,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6807,10 +6811,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6819,19 +6823,19 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6881,39 +6885,39 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6924,7 +6928,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6933,19 +6937,19 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6995,25 +6999,25 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7024,14 +7028,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7050,13 +7054,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7107,7 +7111,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7119,13 +7123,13 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7136,10 +7140,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7159,16 +7163,16 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7219,7 +7223,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7231,27 +7235,27 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7262,7 +7266,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7274,13 +7278,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7331,13 +7335,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7349,7 +7353,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7360,14 +7364,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7386,16 +7390,16 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7445,7 +7449,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7457,13 +7461,13 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7474,14 +7478,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7494,25 +7498,25 @@
         <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7561,7 +7565,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7573,13 +7577,13 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7590,10 +7594,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7613,19 +7617,19 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7651,13 +7655,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7675,7 +7679,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7687,27 +7691,27 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7718,7 +7722,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7730,13 +7734,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7787,39 +7791,39 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7830,7 +7834,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7839,16 +7843,16 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7899,39 +7903,39 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7951,16 +7955,16 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8011,7 +8015,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8023,27 +8027,27 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8051,13 +8055,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
@@ -8066,16 +8070,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8125,39 +8129,39 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8168,7 +8172,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8180,13 +8184,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8237,13 +8241,13 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
@@ -8255,7 +8259,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8266,14 +8270,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8292,16 +8296,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8339,19 +8343,19 @@
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8363,13 +8367,13 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8378,12 +8382,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8391,31 +8395,31 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8465,39 +8469,39 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8508,35 +8512,35 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>79</v>
@@ -8581,39 +8585,39 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8636,16 +8640,16 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8695,43 +8699,43 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8747,19 +8751,19 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8785,13 +8789,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -8809,7 +8813,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8821,31 +8825,31 @@
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8861,19 +8865,19 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8923,7 +8927,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8935,27 +8939,27 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8975,16 +8979,16 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9035,7 +9039,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9047,13 +9051,13 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9064,10 +9068,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9078,7 +9082,7 @@
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9090,13 +9094,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9147,13 +9151,13 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
@@ -9165,7 +9169,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9176,14 +9180,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9202,16 +9206,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9261,7 +9265,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9273,13 +9277,13 @@
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9290,14 +9294,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9310,25 +9314,25 @@
         <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9377,7 +9381,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9389,13 +9393,13 @@
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9406,21 +9410,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9429,19 +9433,19 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9491,39 +9495,39 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9534,7 +9538,7 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -9546,13 +9550,13 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9579,13 +9583,13 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9603,25 +9607,25 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -9632,10 +9636,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9646,7 +9650,7 @@
         <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -9658,13 +9662,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9715,25 +9719,25 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -9744,10 +9748,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9770,16 +9774,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9829,7 +9833,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9841,13 +9845,13 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -9858,10 +9862,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9884,16 +9888,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9943,25 +9947,25 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -9972,10 +9976,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9986,7 +9990,7 @@
         <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
@@ -9998,13 +10002,13 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10055,13 +10059,13 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
@@ -10073,7 +10077,7 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
@@ -10084,14 +10088,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10110,16 +10114,16 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10169,7 +10173,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10181,13 +10185,13 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -10198,14 +10202,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10218,25 +10222,25 @@
         <v>79</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10285,7 +10289,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10297,13 +10301,13 @@
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
@@ -10314,10 +10318,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10328,7 +10332,7 @@
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10340,13 +10344,13 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10397,39 +10401,39 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10440,7 +10444,7 @@
         <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>79</v>
@@ -10452,13 +10456,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10509,25 +10513,25 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
@@ -10538,10 +10542,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10552,7 +10556,7 @@
         <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
@@ -10564,13 +10568,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10597,13 +10601,13 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -10621,39 +10625,39 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10664,7 +10668,7 @@
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>79</v>
@@ -10676,13 +10680,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10709,13 +10713,13 @@
         <v>79</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>79</v>
@@ -10733,39 +10737,39 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10788,19 +10792,19 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -10825,13 +10829,13 @@
         <v>79</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -10849,7 +10853,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10861,27 +10865,27 @@
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10904,13 +10908,13 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10937,13 +10941,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -10961,7 +10965,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10973,27 +10977,27 @@
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11016,13 +11020,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11049,13 +11053,13 @@
         <v>79</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>79</v>
@@ -11073,7 +11077,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11085,27 +11089,27 @@
         <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11116,7 +11120,7 @@
         <v>77</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>79</v>
@@ -11128,13 +11132,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11185,39 +11189,39 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11228,7 +11232,7 @@
         <v>77</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11240,13 +11244,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11273,13 +11277,13 @@
         <v>79</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -11297,39 +11301,39 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11352,16 +11356,16 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11411,7 +11415,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11423,13 +11427,13 @@
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
@@ -11440,10 +11444,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11454,7 +11458,7 @@
         <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>79</v>
@@ -11466,13 +11470,13 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11523,13 +11527,13 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>79</v>
@@ -11541,7 +11545,7 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
@@ -11552,14 +11556,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11578,16 +11582,16 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11637,7 +11641,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11649,13 +11653,13 @@
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>79</v>
@@ -11666,14 +11670,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11686,25 +11690,25 @@
         <v>79</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -11753,7 +11757,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11765,13 +11769,13 @@
         <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>79</v>
@@ -11782,10 +11786,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11793,10 +11797,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>79</v>
@@ -11808,13 +11812,13 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11865,39 +11869,39 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11908,7 +11912,7 @@
         <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>79</v>
@@ -11920,16 +11924,16 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11955,13 +11959,13 @@
         <v>79</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>79</v>
@@ -11979,25 +11983,25 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>79</v>
@@ -12008,10 +12012,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12022,7 +12026,7 @@
         <v>77</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>79</v>
@@ -12034,16 +12038,16 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12069,13 +12073,13 @@
         <v>79</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>79</v>
@@ -12093,19 +12097,19 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
@@ -12122,10 +12126,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12136,7 +12140,7 @@
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>79</v>
@@ -12148,13 +12152,13 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12205,25 +12209,25 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>79</v>
@@ -12232,12 +12236,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12245,13 +12249,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>79</v>
@@ -12260,13 +12264,13 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12317,39 +12321,39 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12372,16 +12376,16 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12431,25 +12435,25 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
@@ -12460,12 +12464,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN92">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
